--- a/Success Plan Sample Customer Data.xlsx
+++ b/Success Plan Sample Customer Data.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="207">
   <si>
     <t xml:space="preserve">Success Plan Generator — Sample Data Source</t>
   </si>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Contents</t>
   </si>
   <si>
-    <t xml:space="preserve">TSIA Success Plan Component</t>
+    <t xml:space="preserve">Success Plan Section</t>
   </si>
   <si>
     <t xml:space="preserve">Typical CSP source table</t>
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Success Metrics</t>
   </si>
   <si>
-    <t xml:space="preserve">Adoption, onboarding, and business-impact metrics vs. target</t>
+    <t xml:space="preserve">Customer-facing outcomes vs. target: time saved, cost reduced, revenue gained, or process simplified</t>
   </si>
   <si>
     <t xml:space="preserve">Scorecard / Outcomes object</t>
@@ -501,19 +501,10 @@
     <t xml:space="preserve">unit</t>
   </si>
   <si>
-    <t xml:space="preserve">Weekly active clinical users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time-to-first-value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">days</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Impact</t>
+    <t xml:space="preserve">higher_is_better</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time Saved</t>
   </si>
   <si>
     <t xml:space="preserve">Patient onboarding time reduction</t>
@@ -522,19 +513,49 @@
     <t xml:space="preserve">% reduction</t>
   </si>
   <si>
-    <t xml:space="preserve">Exception alerts actioned within SLA</t>
+    <t xml:space="preserve">Process Simplified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy scheduling tools consolidated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost Reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administrative cost savings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$/year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exception-handling time reduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freight exception cost avoided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual exception reviews eliminated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reviews/week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-serve report requests deflected</t>
   </si>
   <si>
     <t xml:space="preserve">%</t>
   </si>
   <si>
-    <t xml:space="preserve">Exception-handling time reduction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly active dashboard users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Self-serve report requests deflected</t>
+    <t xml:space="preserve">Analyst hours saved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hours/month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legacy BI licensing costs avoided</t>
   </si>
   <si>
     <t xml:space="preserve">owner</t>
@@ -770,52 +791,56 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1074,168 +1099,168 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1261,131 +1286,131 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>186000</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="I2" s="8" t="n">
+      <c r="I2" s="9" t="n">
         <f aca="false">F2-DATE(2026,9,11)</f>
         <v>157</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>64000</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" s="10" t="n">
         <f aca="false">F3-DATE(2026,9,11)</f>
         <v>80</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>221000</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="I4" s="9" t="n">
         <f aca="false">F4-DATE(2026,9,11)</f>
         <v>232</v>
       </c>
@@ -1409,146 +1434,146 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1571,135 +1596,135 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1722,171 +1747,171 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="11" t="n">
         <v>0.92</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="6" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="12" t="n">
         <v>0.61</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="11" t="n">
         <v>0.34</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>0.28</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <v>0.71</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>0.83</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1909,196 +1934,196 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2118,194 +2143,244 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>156</v>
       </c>
+      <c r="G1" s="8" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>640</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>900</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>158</v>
       </c>
+      <c r="C2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="G5" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>38000</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="C7" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="C10" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>340</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>165</v>
+      <c r="G10" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2327,144 +2402,144 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="B1" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>174</v>
+      <c r="E2" s="6" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>178</v>
+      <c r="B3" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>178</v>
+      <c r="C4" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>178</v>
+      <c r="C6" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="B7" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="B8" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2487,95 +2562,95 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>191</v>
+      <c r="B1" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>193</v>
+      <c r="E2" s="6" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>195</v>
+      <c r="E3" s="5" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>197</v>
+      <c r="E4" s="6" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>199</v>
+      <c r="E5" s="5" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
